--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484163_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484163_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5118</v>
+        <v>6.9252</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2688</v>
+        <v>2.9627</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2431</v>
+        <v>3.9625</v>
       </c>
       <c r="G2" t="n">
         <v>1.7126</v>
@@ -610,13 +610,13 @@
         <v>3.1741</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9182</v>
+        <v>0.3316</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3629</v>
+        <v>0.0568</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5554</v>
+        <v>0.2748</v>
       </c>
       <c r="V2" t="n">
         <v>3.6907</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. TERREROS RIVAS</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9632</v>
+        <v>3.127</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6744</v>
+        <v>0.5121</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2888</v>
+        <v>2.6149</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7689</v>
+        <v>3.8317</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4892</v>
+        <v>2.4998</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2581</v>
+        <v>1.3318</v>
       </c>
       <c r="J3" t="n">
-        <v>1.538</v>
+        <v>4.5368</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3682</v>
+        <v>2.6868</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1698</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2309</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.187</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0883</v>
+        <v>-0.5182</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5871</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q3" t="n">
         <v>-3.9677</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>2.9758</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3685</v>
+        <v>0.0213</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4252</v>
+        <v>-0.323</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0567</v>
+        <v>0.3443</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4129</v>
+        <v>0.266</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6789</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>I. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5429</v>
+        <v>2.5551</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1001</v>
+        <v>0.2663</v>
       </c>
       <c r="F4" t="n">
-        <v>2.643</v>
+        <v>2.2888</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8317</v>
+        <v>1.7689</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4998</v>
+        <v>-0.4892</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3318</v>
+        <v>2.2581</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5368</v>
+        <v>1.538</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6868</v>
+        <v>0.3682</v>
       </c>
       <c r="L4" t="n">
-        <v>1.85</v>
+        <v>1.1698</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.2309</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.187</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5182</v>
+        <v>1.0883</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9919</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q4" t="n">
         <v>-3.9677</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9758</v>
+        <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5629</v>
+        <v>-0.0396</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9352</v>
+        <v>0.0171</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3723</v>
+        <v>-0.0567</v>
       </c>
       <c r="V4" t="n">
-        <v>0.266</v>
+        <v>2.4129</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>2.6789</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3353</v>
+        <v>2.1818</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9898</v>
+        <v>2.0298</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3455</v>
+        <v>0.152</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6246</v>
+        <v>1.7756</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7014</v>
+        <v>0.2676</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0768</v>
+        <v>1.508</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6837</v>
+        <v>1.4726</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9638</v>
+        <v>0.7873</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2801</v>
+        <v>0.6853</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.059</v>
+        <v>0.303</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2623</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7967</v>
+        <v>0.8227</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7187</v>
+        <v>-0.5895</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3061</v>
+        <v>-0.2607</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4126</v>
+        <v>-0.3288</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.0044</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. DIOP</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8468</v>
+        <v>1.917</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9696</v>
+        <v>1.6837</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1228</v>
+        <v>0.2333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7405</v>
+        <v>0.6246</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3209</v>
+        <v>2.7014</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5804</v>
+        <v>-2.0768</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6635</v>
+        <v>1.6837</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5832</v>
+        <v>2.9638</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0803</v>
+        <v>-1.2801</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.923</v>
+        <v>-1.059</v>
       </c>
       <c r="N6" t="n">
         <v>-0.2623</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6607</v>
+        <v>-0.7967</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5192</v>
+        <v>0.3004</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3061</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2131</v>
+        <v>0.3004</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>C. DIOP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5696</v>
+        <v>1.5968</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4176</v>
+        <v>1.6636</v>
       </c>
       <c r="F7" t="n">
-        <v>0.152</v>
+        <v>-0.0667</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7756</v>
+        <v>0.7405</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2676</v>
+        <v>1.3209</v>
       </c>
       <c r="I7" t="n">
-        <v>1.508</v>
+        <v>-0.5804</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4726</v>
+        <v>1.6635</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7873</v>
+        <v>1.5832</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6853</v>
+        <v>0.0803</v>
       </c>
       <c r="M7" t="n">
-        <v>0.303</v>
+        <v>-0.923</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.2623</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8227</v>
+        <v>-0.6607</v>
       </c>
       <c r="P7" t="n">
         <v>1.1903</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2017</v>
+        <v>0.2692</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8728</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3288</v>
+        <v>0.2692</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1947</v>
+        <v>-0.6032</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.0044</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3401</v>
+        <v>0.8528</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4026</v>
+        <v>-1.1986</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7428</v>
+        <v>2.0514</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0418</v>
@@ -1078,13 +1078,13 @@
         <v>2.3806</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7408</v>
+        <v>-0.2281</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1303</v>
+        <v>0.0738</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6105</v>
+        <v>-0.3019</v>
       </c>
       <c r="V8" t="n">
         <v>-0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1968</v>
+        <v>-1.1814</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6425</v>
+        <v>-1.4588</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4457</v>
+        <v>0.2774</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9631</v>
@@ -1156,13 +1156,13 @@
         <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1631</v>
+        <v>0.1786</v>
       </c>
       <c r="T9" t="n">
-        <v>0.924</v>
+        <v>0.1077</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2392</v>
+        <v>0.0708</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8217</v>
+        <v>-2.3472</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8369</v>
+        <v>-1.5308</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9848</v>
+        <v>-0.8165</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0627</v>
@@ -1234,13 +1234,13 @@
         <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.806</v>
+        <v>-0.3316</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6858</v>
+        <v>-0.3797</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1202</v>
+        <v>0.0481</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7384</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8428</v>
+        <v>-4.3786</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5213</v>
+        <v>-3.1131</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3215</v>
+        <v>-1.2654</v>
       </c>
       <c r="G11" t="n">
         <v>-2.411</v>
@@ -1312,13 +1312,13 @@
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9432</v>
+        <v>-0.4789</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7481</v>
+        <v>-0.34</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.195</v>
+        <v>-0.1389</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6789</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.2484</v>
+        <v>11.2485</v>
       </c>
       <c r="E12" t="n">
-        <v>1.816800000000001</v>
+        <v>1.8169</v>
       </c>
       <c r="F12" t="n">
-        <v>9.431799999999999</v>
+        <v>9.431700000000001</v>
       </c>
       <c r="G12" t="n">
         <v>4.975300000000001</v>
@@ -1363,7 +1363,7 @@
         <v>4.0161</v>
       </c>
       <c r="J12" t="n">
-        <v>7.723000000000003</v>
+        <v>7.723000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>5.1972</v>
@@ -1375,7 +1375,7 @@
         <v>-2.7477</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.238099999999999</v>
+        <v>-4.2381</v>
       </c>
       <c r="O12" t="n">
         <v>1.4904</v>
@@ -1390,13 +1390,13 @@
         <v>18.8465</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5669000000000002</v>
+        <v>-0.5666</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0479</v>
+        <v>-1.048</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4814</v>
+        <v>0.4813000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0.8883999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.062</v>
+        <v>4.4396</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9755</v>
+        <v>3.4654</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0864</v>
+        <v>0.9742</v>
       </c>
       <c r="G13" t="n">
         <v>1.8093</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1155</v>
+        <v>0.4931</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7993</v>
+        <v>0.2891</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3162</v>
+        <v>0.204</v>
       </c>
       <c r="V13" t="n">
         <v>0.7486</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0202</v>
+        <v>2.908</v>
       </c>
       <c r="E14" t="n">
         <v>0.0569</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9633</v>
+        <v>2.8511</v>
       </c>
       <c r="G14" t="n">
         <v>1.5368</v>
@@ -1546,13 +1546,13 @@
         <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0272</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2766</v>
+        <v>0.1643</v>
       </c>
       <c r="V14" t="n">
         <v>0.266</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7139</v>
+        <v>0.5229</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2929</v>
+        <v>-0.8691</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.579</v>
+        <v>1.392</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1774</v>
+        <v>0.1374</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2814</v>
+        <v>0.5391</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4588</v>
+        <v>-0.4016</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0588</v>
+        <v>-0.6197</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7339</v>
+        <v>0.0605</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6751</v>
+        <v>-0.6802</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2362</v>
+        <v>0.7572</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4525</v>
+        <v>0.4786</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7837</v>
+        <v>0.2786</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1822</v>
+        <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2897</v>
+        <v>-0.2097</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4876</v>
+        <v>-0.2494</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1979</v>
+        <v>0.0396</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4113</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5229</v>
+        <v>0.5022</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8691</v>
+        <v>1.8847</v>
       </c>
       <c r="F16" t="n">
-        <v>1.392</v>
+        <v>-1.3826</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1374</v>
+        <v>-1.1774</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5391</v>
+        <v>0.2814</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4016</v>
+        <v>-1.4588</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6197</v>
+        <v>1.0588</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0605</v>
+        <v>1.7339</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6802</v>
+        <v>-0.6751</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7572</v>
+        <v>-2.2362</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4786</v>
+        <v>-1.4525</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2786</v>
+        <v>-0.7837</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5952</v>
+        <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2097</v>
+        <v>0.0779</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2494</v>
+        <v>0.0794</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0396</v>
+        <v>-0.0015</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4113</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9557</v>
+        <v>-0.2977</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.793</v>
+        <v>-0.0788</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1628</v>
+        <v>-0.2189</v>
       </c>
       <c r="G17" t="n">
         <v>-1.7668</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1338</v>
+        <v>0.5243</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4897</v>
+        <v>0.4335</v>
       </c>
       <c r="V17" t="n">
         <v>1.7384</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8304</v>
+        <v>-1.532</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7348</v>
+        <v>-2.6328</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9044</v>
+        <v>1.1008</v>
       </c>
       <c r="G18" t="n">
         <v>-2.169</v>
@@ -1858,13 +1858,13 @@
         <v>2.3806</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2035</v>
+        <v>0.0949</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0056</v>
+        <v>0.0964</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1979</v>
+        <v>-0.0015</v>
       </c>
       <c r="V18" t="n">
         <v>0.1453</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2727</v>
+        <v>-2.8162</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9413</v>
+        <v>-0.7372</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3315</v>
+        <v>-2.079</v>
       </c>
       <c r="G19" t="n">
         <v>0.1828</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2057</v>
+        <v>0.2508</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0056</v>
+        <v>0.1985</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2001</v>
+        <v>0.0524</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8692</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9003</v>
+        <v>-3.834</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.807</v>
+        <v>-2.909</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0933</v>
+        <v>-0.925</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2813</v>
@@ -2014,13 +2014,13 @@
         <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1258</v>
+        <v>-0.0595</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0056</v>
+        <v>-0.1076</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1202</v>
+        <v>0.0481</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1206</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1803</v>
+        <v>-4.0961</v>
       </c>
       <c r="E21" t="n">
         <v>-3.2713</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9089</v>
+        <v>-0.8248</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3149</v>
@@ -2092,13 +2092,13 @@
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0718</v>
+        <v>-0.9877</v>
       </c>
       <c r="T21" t="n">
         <v>-0.6235000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4484</v>
+        <v>-0.3642</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.428</v>
+        <v>-7.0453</v>
       </c>
       <c r="E22" t="n">
         <v>-4.3405</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0875</v>
+        <v>-2.7047</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9322</v>
@@ -2170,13 +2170,13 @@
         <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0848</v>
+        <v>0.4676</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0056</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0904</v>
+        <v>0.4732</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0016</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.2484</v>
+        <v>-11.2486</v>
       </c>
       <c r="E23" t="n">
         <v>-9.431699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.816900000000001</v>
+        <v>-1.8169</v>
       </c>
       <c r="G23" t="n">
         <v>-4.975300000000001</v>
@@ -2248,13 +2248,13 @@
         <v>12.8951</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5668999999999997</v>
+        <v>0.5667</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4813000000000001</v>
+        <v>-0.4813</v>
       </c>
       <c r="U23" t="n">
-        <v>1.048</v>
+        <v>1.0479</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8882999999999999</v>
